--- a/out/Petra Speech Logs 2024-09 and 10 Sept & Oct - 9 weeks 15 sessions, 10-15 SLP absent_cleaned.xlsx
+++ b/out/Petra Speech Logs 2024-09 and 10 Sept & Oct - 9 weeks 15 sessions, 10-15 SLP absent_cleaned.xlsx
@@ -472,13 +472,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
@@ -496,17 +496,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Week of (Monday)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date of Service</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Day of Week</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Week of (Monday)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -553,17 +553,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>09/02/2024</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>09/03/2024</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>09/02/2024</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -610,19 +610,19 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>09/09/2024</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>09/10/2024</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>09/09/2024</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Start 10:45am - End 11:15am</t>
@@ -635,7 +635,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>09/09/2024</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>09/10/2024</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>09/09/2024</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -724,19 +724,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>09/16/2024</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>09/17/2024</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>09/16/2024</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Start 9:30am - End 10:00am</t>
@@ -749,7 +749,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -781,17 +781,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>09/16/2024</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>09/17/2024</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>09/16/2024</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>09/23/2024</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>09/24/2024</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>09/23/2024</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Start 9:30am - End 10:00am</t>
@@ -863,7 +863,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -895,19 +895,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>10/01/2024</t>
+          <t>09/23/2024</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>09/24/2024</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>09/30/2024</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Start 10:30am - End 11:00am</t>
@@ -920,17 +920,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>"Ten Apples Up on Top" skills targeted: following directions "put on..." making choices (put on me, put on friend) I like ___ yes/no questions Used device to express opinion used voice to request "put on me" or "put on friend" w/ model</t>
+          <t>"Time for School Little Blue Truck" labeling animals w/ carrier phrase modeled "I see..." follow directions "put (animal) in" or "take (animal) out" where is...? responded with location w/ visual</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -952,105 +952,109 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>10/08/2024</t>
+          <t>09/30/2024</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>10/01/2024</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10/07/2024</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Start 10:30am - End 11:00am</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>G - Groups</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>"Ten Apples Up on Top" skills targeted: following directions "put on..." making choices (put on me, put on friend) I like ___ yes/no questions Used device to express opinion used voice to request "put on me" or "put on friend" w/ model</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Petra Lingling Bloomer</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>09/30/2024</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10/01/2024</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>Start 9:30am - End 10:00am</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>supported morning meeting: responding to daily academic questions re: weather, date, where are you? home/school, who is here? labeling classmates.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Supported during morning meeting -- Petra was able to respond to questions when provided multiple prompts and attention-gaining strategies. She was focused on desired task (coloring) and had difficulty transitioning.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Petra Lingling Bloomer</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>10/15/2024</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>10/14/2024</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Start 3:25pm - End 3:25pm</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>D - Clinician/Therapist Absent</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>No Goal</t>
         </is>
       </c>
     </row>
@@ -1062,22 +1066,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/22/2024</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10/08/2024</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10/21/2024</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Start 9:30am - End 10:30am</t>
+          <t>Start 9:30am - End 10:00am</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1087,12 +1091,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9:30-10:00 supported during morning meeting: greetings, answering daily questions, responding to communication attempts, requesting more (bubbles), following classroom directions 10:00-10:30 There Was an Old Lady Who Swallowed Some Leaves: labeling - able to label all vocab on AAC or voice "eat ___" 2 word utterances</t>
+          <t>supported morning meeting: responding to daily academic questions re: weather, date, where are you? home/school, who is here? labeling classmates.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1119,50 +1123,217 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>10/07/2024</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2024</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Start 10:30am - End 11:00am</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>G - Groups</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Target words/phrases: big, help, look under __ Who? w/ visual choices and exp using AAC What? verbalized answer</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Petra Lingling Bloomer</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>10/14/2024</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>10/15/2024</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Start 3:25pm - End 3:25pm</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>D - Clinician/Therapist Absent</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>No Goal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Petra Lingling Bloomer</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>10/21/2024</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10/22/2024</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Start 9:30am - End 10:30am</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>G - Groups</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>supported during morning meeting: greetings, answering daily questions, responding to communication attempts, requesting more (bubbles), following classroom directions 10:00-10:30 There Was an Old Lady Who Swallowed Some Leaves: labeling - able to label all vocab on AAC or voice "eat ___" 2 word utterances</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Petra Lingling Bloomer</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>10/28/2024</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>10/29/2024</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10/28/2024</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Start 9:45am - End 10:45am</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9:45-10:15am: Supported during morning meeting greetings - responded with voice and AAC making requests (I want cheerios) 4x, and gaining attention (model) with gesture. 10:30-11:00am: 5 sessions group lesson identifying descriptors of 5 senses with model expressing in sentences w/ model</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>: Supported during morning meeting greetings - responded with voice and AAC making requests (I want cheerios) 4x, and gaining attention (model) with gesture. 10:30-11:00am: 5 sessions group lesson identifying descriptors of 5 senses with model expressing in sentences w/ model</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>

--- a/out/Petra Speech Logs 2024-09 and 10 Sept & Oct - 9 weeks 15 sessions, 10-15 SLP absent_cleaned.xlsx
+++ b/out/Petra Speech Logs 2024-09 and 10 Sept & Oct - 9 weeks 15 sessions, 10-15 SLP absent_cleaned.xlsx
@@ -1208,7 +1208,11 @@
           <t>(LEFT BLANK)</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
